--- a/data/trans_orig/IP1012-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87617</t>
+          <t>87610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174494</t>
+          <t>174480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468811</t>
+          <t>468744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>475644</t>
+          <t>475590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>884633</t>
+          <t>884781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891737</t>
+          <t>891732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169269</t>
+          <t>169312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152458</t>
+          <t>152904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324874</t>
+          <t>324440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330904</t>
+          <t>330924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>675700</t>
+          <t>675622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>680392</t>
+          <t>680386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>710617</t>
+          <t>711139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719357</t>
+          <t>719322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1389645</t>
+          <t>1389929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1399079</t>
+          <t>1398899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78242</t>
+          <t>77847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170334</t>
+          <t>170041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>442096</t>
+          <t>443390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449040</t>
+          <t>449043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484971</t>
+          <t>484279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491708</t>
+          <t>491716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>931469</t>
+          <t>930925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940093</t>
+          <t>939846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159853</t>
+          <t>160403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167152</t>
+          <t>167627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>330237</t>
+          <t>331257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>699257</t>
+          <t>698681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>706010</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>735789</t>
+          <t>736285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>745682</t>
+          <t>745644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1438976</t>
+          <t>1438759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1450057</t>
+          <t>1449798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485632</t>
+          <t>485634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>957927</t>
+          <t>957929</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181929</t>
+          <t>181756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354395</t>
+          <t>353719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>738470</t>
+          <t>738013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744135</t>
+          <t>744121</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1442369</t>
+          <t>1442258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448501</t>
+          <t>1448505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1012-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,92 +722,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90225</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87610</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>87604</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>265</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174480</t>
+          <t>174476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8804</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>3723</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8247</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3723</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>473268</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>468187</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>475475</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>473268</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>468744</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>475590</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1342</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>884781</t>
+          <t>884954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891732</t>
+          <t>891726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1367</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4754</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5234</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156172</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>152850</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157497</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172699</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>169312</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169638</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156172</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>152904</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>157494</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>485</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324440</t>
+          <t>324778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330924</t>
+          <t>330895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10712</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5399</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5643</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2652</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10835</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>716285</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>711262</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>719267</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679012</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>675622</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>680386</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>675378</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>680387</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1077</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>716285</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>711139</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>719322</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2092</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1389929</t>
+          <t>1389159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1398899</t>
+          <t>1398992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6671</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1831</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6496</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6231</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82512</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>77672</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84343</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82512</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>77847</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84343</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170041</t>
+          <t>170001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84343</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84343</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84343</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84343</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84343</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84343</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7752</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2318</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6310</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2969</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8125</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>489435</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>484652</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>491713</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>447382</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>443390</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>449043</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>443515</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>449044</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,85%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>489435</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>484279</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>491716</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1349</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>930925</t>
+          <t>931063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939846</t>
+          <t>939877</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4890</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4937</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3934</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170289</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>166671</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>164414</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160403</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>160722</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170289</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167627</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>474</t>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331257</t>
+          <t>330802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336279</t>
+          <t>336284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2913</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12131</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3243</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8247</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2663</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12022</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742235</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>736176</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>745394</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>703685</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>698681</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>706006</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>699189</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>706005</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,87%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742235</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>736285</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>745644</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2072</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1438759</t>
+          <t>1438328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1449798</t>
+          <t>1450319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>748307</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>748307</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>748307</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>748307</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>748307</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>748307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4276,102 +4276,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3390</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3101</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3096</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488117</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>485345</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488117</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>485634</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1407</t>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>957929</t>
+          <t>957468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,92 +4614,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6256</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2118</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5739</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>185377</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>181239</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>186849</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>185377</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>181756</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>186850</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>526</t>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>353719</t>
+          <t>353504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359553</t>
+          <t>359548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,92 +4957,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6647</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2736</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6831</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742108</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>738197</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744133</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742108</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>738013</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744121</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2121</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1442258</t>
+          <t>1442525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1448505</t>
+          <t>1448503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
